--- a/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0003T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0003T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.47329144661791</v>
+        <v>2.514409860075411</v>
       </c>
       <c r="D2" t="n">
-        <v>16.59404295733726</v>
+        <v>2.696531980567305</v>
       </c>
       <c r="E2" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F2" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.47235775283351</v>
+        <v>4.464258134835445</v>
       </c>
       <c r="D3" t="n">
-        <v>25.52019995981001</v>
+        <v>4.147032493469127</v>
       </c>
       <c r="E3" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F3" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.0965653880566</v>
+        <v>5.703191875559198</v>
       </c>
       <c r="D4" t="n">
-        <v>35.59841115913138</v>
+        <v>5.78474181335885</v>
       </c>
       <c r="E4" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F4" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.1325453731388</v>
+        <v>4.246538623135056</v>
       </c>
       <c r="D5" t="n">
-        <v>26.50743882294186</v>
+        <v>4.307458808728052</v>
       </c>
       <c r="E5" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F5" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.55527965861596</v>
+        <v>5.290232944525093</v>
       </c>
       <c r="D6" t="n">
-        <v>25.89699816366539</v>
+        <v>4.208262201595627</v>
       </c>
       <c r="E6" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F6" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>39.16581537715649</v>
+        <v>6.36444499878793</v>
       </c>
       <c r="D7" t="n">
-        <v>36.74264201731155</v>
+        <v>5.970679327813126</v>
       </c>
       <c r="E7" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F7" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>20.34684531022135</v>
+        <v>3.30636236291097</v>
       </c>
       <c r="D8" t="n">
-        <v>8.047852384613863</v>
+        <v>1.307776012499753</v>
       </c>
       <c r="E8" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F8" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>47.79026187775515</v>
+        <v>7.765917555135212</v>
       </c>
       <c r="D9" t="n">
-        <v>48.47738106549834</v>
+        <v>7.877574423143479</v>
       </c>
       <c r="E9" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F9" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>48.35415280443608</v>
+        <v>7.857549830720864</v>
       </c>
       <c r="D10" t="n">
-        <v>48.12685381580777</v>
+        <v>7.820613745068763</v>
       </c>
       <c r="E10" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F10" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>51.75855060066169</v>
+        <v>8.410764472607525</v>
       </c>
       <c r="D11" t="n">
-        <v>52.27152965412879</v>
+        <v>8.49412356879593</v>
       </c>
       <c r="E11" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F11" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>67.48090094063058</v>
+        <v>10.96564640285247</v>
       </c>
       <c r="D12" t="n">
-        <v>64.09743349942897</v>
+        <v>10.41583294365721</v>
       </c>
       <c r="E12" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F12" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>65.40596314576058</v>
+        <v>10.62846901118609</v>
       </c>
       <c r="D13" t="n">
-        <v>64.07960814920419</v>
+        <v>10.41293632424568</v>
       </c>
       <c r="E13" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F13" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>13.07915185052042</v>
+        <v>2.125362175709568</v>
       </c>
       <c r="D14" t="n">
-        <v>12.3325357398656</v>
+        <v>2.00403705772816</v>
       </c>
       <c r="E14" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F14" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>28.03353973638915</v>
+        <v>4.555450207163236</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30102869699315</v>
+        <v>4.598917163261388</v>
       </c>
       <c r="E15" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F15" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>70.22903207654927</v>
+        <v>11.41221771243926</v>
       </c>
       <c r="D16" t="n">
-        <v>69.65384787373591</v>
+        <v>11.31875027948209</v>
       </c>
       <c r="E16" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F16" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>52.68293123479085</v>
+        <v>8.560976325653513</v>
       </c>
       <c r="D17" t="n">
-        <v>52.90713093217821</v>
+        <v>8.597408776478959</v>
       </c>
       <c r="E17" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F17" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>60.23191779117896</v>
+        <v>9.78768664106658</v>
       </c>
       <c r="D18" t="n">
-        <v>59.56467675587755</v>
+        <v>9.679259972830103</v>
       </c>
       <c r="E18" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F18" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>34.96829678381114</v>
+        <v>5.68234822736931</v>
       </c>
       <c r="D19" t="n">
-        <v>34.2205487134105</v>
+        <v>5.560839165929207</v>
       </c>
       <c r="E19" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F19" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>67.18435479113388</v>
+        <v>10.91745765355926</v>
       </c>
       <c r="D20" t="n">
-        <v>66.49646585889248</v>
+        <v>10.80567570207003</v>
       </c>
       <c r="E20" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F20" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>45.29625153002691</v>
+        <v>7.360640873629374</v>
       </c>
       <c r="D21" t="n">
-        <v>45.17590210026628</v>
+        <v>7.341084091293271</v>
       </c>
       <c r="E21" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F21" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>47.96957502076548</v>
+        <v>7.79505594087439</v>
       </c>
       <c r="D22" t="n">
-        <v>47.22924109710232</v>
+        <v>7.674751678279127</v>
       </c>
       <c r="E22" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F22" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>57.84548577015673</v>
+        <v>9.399891437650469</v>
       </c>
       <c r="D23" t="n">
-        <v>57.75054220820339</v>
+        <v>9.384463108833051</v>
       </c>
       <c r="E23" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F23" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>56.42329868249755</v>
+        <v>9.168786035905852</v>
       </c>
       <c r="D24" t="n">
-        <v>55.67596945037792</v>
+        <v>9.047345035686412</v>
       </c>
       <c r="E24" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F24" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>44.59449871585851</v>
+        <v>7.246606041327008</v>
       </c>
       <c r="D25" t="n">
-        <v>44.02034691859514</v>
+        <v>7.15330637427171</v>
       </c>
       <c r="E25" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F25" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>51.99347410044783</v>
+        <v>8.448939541322773</v>
       </c>
       <c r="D26" t="n">
-        <v>51.63544521452796</v>
+        <v>8.390759847360792</v>
       </c>
       <c r="E26" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F26" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>55.36525718550349</v>
+        <v>8.996854292644317</v>
       </c>
       <c r="D27" t="n">
-        <v>54.92396099071903</v>
+        <v>8.925143660991843</v>
       </c>
       <c r="E27" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F27" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>55.91442099690411</v>
+        <v>9.086093411996918</v>
       </c>
       <c r="D28" t="n">
-        <v>55.32176186417</v>
+        <v>8.989786302927625</v>
       </c>
       <c r="E28" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F28" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>61.34917325005551</v>
+        <v>9.969240653134021</v>
       </c>
       <c r="D29" t="n">
-        <v>60.64674587620871</v>
+        <v>9.855096204883916</v>
       </c>
       <c r="E29" t="n">
-        <v>15.89721052022496</v>
+        <v>2.583296709536556</v>
       </c>
       <c r="F29" t="n">
-        <v>16.68687123061049</v>
+        <v>2.711616574974204</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
